--- a/load-tests/Full_Test_Suite_Report_300+.xlsx
+++ b/load-tests/Full_Test_Suite_Report_300+.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="1093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3321" uniqueCount="1234">
   <si>
     <t>🧪 Medicate App — Full Test Suite Summary Report</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Test Report Date</t>
   </si>
   <si>
-    <t>8/10/2026, 10:57:46 pm</t>
+    <t>8/10/2026, 10:59:23 pm</t>
   </si>
   <si>
     <t>Tester</t>
@@ -264,9 +264,6 @@
     <t>Empty credentials should work correctly without errors</t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>WEB-005</t>
   </si>
   <si>
@@ -557,6 +554,9 @@
   </si>
   <si>
     <t>User name displayed should work correctly without errors</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>WEB-025</t>
@@ -2607,10 +2607,10 @@
     <t>LOAD-031</t>
   </si>
   <si>
-    <t>Spike (200 VUs)</t>
-  </si>
-  <si>
-    <t>Spike (200 VUs) — GET /api/security/stats — Run 1</t>
+    <t>Spike Test (200 VUs)</t>
+  </si>
+  <si>
+    <t>Spike Test (200 VUs) — GET /api/security/stats — Run 1</t>
   </si>
   <si>
     <t>k6 installed, API running, 200 VUs configured</t>
@@ -2625,19 +2625,19 @@
     <t>LOAD-032</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/stats — Run 2</t>
+    <t>Spike Test (200 VUs) — GET /api/security/stats — Run 2</t>
   </si>
   <si>
     <t>LOAD-033</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/stats — Run 3</t>
+    <t>Spike Test (200 VUs) — GET /api/security/stats — Run 3</t>
   </si>
   <si>
     <t>LOAD-034</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/events/recent — Run 1</t>
+    <t>Spike Test (200 VUs) — GET /api/security/events/recent — Run 1</t>
   </si>
   <si>
     <t xml:space="preserve">1. Start k6 with 200 VUs
@@ -2649,19 +2649,19 @@
     <t>LOAD-035</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/events/recent — Run 2</t>
+    <t>Spike Test (200 VUs) — GET /api/security/events/recent — Run 2</t>
   </si>
   <si>
     <t>LOAD-036</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/events/recent — Run 3</t>
+    <t>Spike Test (200 VUs) — GET /api/security/events/recent — Run 3</t>
   </si>
   <si>
     <t>LOAD-037</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/alerts — Run 1</t>
+    <t>Spike Test (200 VUs) — GET /api/security/alerts — Run 1</t>
   </si>
   <si>
     <t xml:space="preserve">1. Start k6 with 200 VUs
@@ -2673,19 +2673,19 @@
     <t>LOAD-038</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/alerts — Run 2</t>
+    <t>Spike Test (200 VUs) — GET /api/security/alerts — Run 2</t>
   </si>
   <si>
     <t>LOAD-039</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/alerts — Run 3</t>
+    <t>Spike Test (200 VUs) — GET /api/security/alerts — Run 3</t>
   </si>
   <si>
     <t>LOAD-040</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — POST /api/security/events — Run 1</t>
+    <t>Spike Test (200 VUs) — POST /api/security/events — Run 1</t>
   </si>
   <si>
     <t xml:space="preserve">1. Start k6 with 200 VUs
@@ -2697,19 +2697,19 @@
     <t>LOAD-041</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — POST /api/security/events — Run 2</t>
+    <t>Spike Test (200 VUs) — POST /api/security/events — Run 2</t>
   </si>
   <si>
     <t>LOAD-042</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — POST /api/security/events — Run 3</t>
+    <t>Spike Test (200 VUs) — POST /api/security/events — Run 3</t>
   </si>
   <si>
     <t>LOAD-043</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/events — Run 1</t>
+    <t>Spike Test (200 VUs) — GET /api/security/events — Run 1</t>
   </si>
   <si>
     <t xml:space="preserve">1. Start k6 with 200 VUs
@@ -2721,22 +2721,22 @@
     <t>LOAD-044</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/events — Run 2</t>
+    <t>Spike Test (200 VUs) — GET /api/security/events — Run 2</t>
   </si>
   <si>
     <t>LOAD-045</t>
   </si>
   <si>
-    <t>Spike (200 VUs) — GET /api/security/events — Run 3</t>
+    <t>Spike Test (200 VUs) — GET /api/security/events — Run 3</t>
   </si>
   <si>
     <t>LOAD-046</t>
   </si>
   <si>
-    <t>Soak (50 VUs)</t>
-  </si>
-  <si>
-    <t>Soak (50 VUs) — GET /api/security/stats — Run 1</t>
+    <t>Soak Test (50 VUs)</t>
+  </si>
+  <si>
+    <t>Soak Test (50 VUs) — GET /api/security/stats — Run 1</t>
   </si>
   <si>
     <t>k6 installed, API running, 50 VUs configured</t>
@@ -2751,19 +2751,19 @@
     <t>LOAD-047</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/stats — Run 2</t>
+    <t>Soak Test (50 VUs) — GET /api/security/stats — Run 2</t>
   </si>
   <si>
     <t>LOAD-048</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/stats — Run 3</t>
+    <t>Soak Test (50 VUs) — GET /api/security/stats — Run 3</t>
   </si>
   <si>
     <t>LOAD-049</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/events/recent — Run 1</t>
+    <t>Soak Test (50 VUs) — GET /api/security/events/recent — Run 1</t>
   </si>
   <si>
     <t xml:space="preserve">1. Start k6 with 50 VUs
@@ -2775,19 +2775,19 @@
     <t>LOAD-050</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/events/recent — Run 2</t>
+    <t>Soak Test (50 VUs) — GET /api/security/events/recent — Run 2</t>
   </si>
   <si>
     <t>LOAD-051</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/events/recent — Run 3</t>
+    <t>Soak Test (50 VUs) — GET /api/security/events/recent — Run 3</t>
   </si>
   <si>
     <t>LOAD-052</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/alerts — Run 1</t>
+    <t>Soak Test (50 VUs) — GET /api/security/alerts — Run 1</t>
   </si>
   <si>
     <t xml:space="preserve">1. Start k6 with 50 VUs
@@ -2799,19 +2799,19 @@
     <t>LOAD-053</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/alerts — Run 2</t>
+    <t>Soak Test (50 VUs) — GET /api/security/alerts — Run 2</t>
   </si>
   <si>
     <t>LOAD-054</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/alerts — Run 3</t>
+    <t>Soak Test (50 VUs) — GET /api/security/alerts — Run 3</t>
   </si>
   <si>
     <t>LOAD-055</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — POST /api/security/events — Run 1</t>
+    <t>Soak Test (50 VUs) — POST /api/security/events — Run 1</t>
   </si>
   <si>
     <t xml:space="preserve">1. Start k6 with 50 VUs
@@ -2823,19 +2823,19 @@
     <t>LOAD-056</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — POST /api/security/events — Run 2</t>
+    <t>Soak Test (50 VUs) — POST /api/security/events — Run 2</t>
   </si>
   <si>
     <t>LOAD-057</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — POST /api/security/events — Run 3</t>
+    <t>Soak Test (50 VUs) — POST /api/security/events — Run 3</t>
   </si>
   <si>
     <t>LOAD-058</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/events — Run 1</t>
+    <t>Soak Test (50 VUs) — GET /api/security/events — Run 1</t>
   </si>
   <si>
     <t xml:space="preserve">1. Start k6 with 50 VUs
@@ -2847,13 +2847,481 @@
     <t>LOAD-059</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/events — Run 2</t>
+    <t>Soak Test (50 VUs) — GET /api/security/events — Run 2</t>
   </si>
   <si>
     <t>LOAD-060</t>
   </si>
   <si>
-    <t>Soak (50 VUs) — GET /api/security/events — Run 3</t>
+    <t>Soak Test (50 VUs) — GET /api/security/events — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-061</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs)</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/stats — Run 1</t>
+  </si>
+  <si>
+    <t>k6 installed, API running, 150 VUs configured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 150 VUs
+2. Run for 2m
+3. Hit GET /api/security/stats
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-062</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/stats — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-063</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/stats — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-064</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/events/recent — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 150 VUs
+2. Run for 2m
+3. Hit GET /api/security/events/recent
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-065</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/events/recent — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-066</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/events/recent — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-067</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/alerts — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 150 VUs
+2. Run for 2m
+3. Hit GET /api/security/alerts
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-068</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/alerts — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-069</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/alerts — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-070</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — POST /api/security/events — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 150 VUs
+2. Run for 2m
+3. Hit POST /api/security/events
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-071</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — POST /api/security/events — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-072</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — POST /api/security/events — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-073</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/events — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 150 VUs
+2. Run for 2m
+3. Hit GET /api/security/events
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-074</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/events — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-075</t>
+  </si>
+  <si>
+    <t>Stress Test (150 VUs) — GET /api/security/events — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-076</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs)</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/stats — Run 1</t>
+  </si>
+  <si>
+    <t>k6 installed, API running, 300 VUs configured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 300 VUs
+2. Run for 1m
+3. Hit GET /api/security/stats
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-077</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/stats — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-078</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/stats — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-079</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/events/recent — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 300 VUs
+2. Run for 1m
+3. Hit GET /api/security/events/recent
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-080</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/events/recent — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-081</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/events/recent — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-082</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/alerts — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 300 VUs
+2. Run for 1m
+3. Hit GET /api/security/alerts
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-083</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/alerts — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-084</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/alerts — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-085</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — POST /api/security/events — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 300 VUs
+2. Run for 1m
+3. Hit POST /api/security/events
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-086</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — POST /api/security/events — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-087</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — POST /api/security/events — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-088</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/events — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 300 VUs
+2. Run for 1m
+3. Hit GET /api/security/events
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-089</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/events — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-090</t>
+  </si>
+  <si>
+    <t>Break Point (300 VUs) — GET /api/security/events — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-091</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs)</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/stats — Run 1</t>
+  </si>
+  <si>
+    <t>LOAD-092</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/stats — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-093</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/stats — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-094</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/events/recent — Run 1</t>
+  </si>
+  <si>
+    <t>LOAD-095</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/events/recent — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-096</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/events/recent — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-097</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/alerts — Run 1</t>
+  </si>
+  <si>
+    <t>LOAD-098</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/alerts — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-099</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/alerts — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-100</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — POST /api/security/events — Run 1</t>
+  </si>
+  <si>
+    <t>LOAD-101</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — POST /api/security/events — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-102</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — POST /api/security/events — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-103</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/events — Run 1</t>
+  </si>
+  <si>
+    <t>LOAD-104</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/events — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-105</t>
+  </si>
+  <si>
+    <t>Recovery Test (100→0 VUs) — GET /api/security/events — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-106</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs)</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/stats — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 100 VUs
+2. Run for 3m
+3. Hit GET /api/security/stats
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-107</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/stats — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-108</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/stats — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-109</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/events/recent — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 100 VUs
+2. Run for 3m
+3. Hit GET /api/security/events/recent
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-110</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/events/recent — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-111</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/events/recent — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-112</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/alerts — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 100 VUs
+2. Run for 3m
+3. Hit GET /api/security/alerts
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-113</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/alerts — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-114</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/alerts — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-115</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — POST /api/security/events — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 100 VUs
+2. Run for 3m
+3. Hit POST /api/security/events
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-116</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — POST /api/security/events — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-117</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — POST /api/security/events — Run 3</t>
+  </si>
+  <si>
+    <t>LOAD-118</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/events — Run 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Start k6 with 100 VUs
+2. Run for 3m
+3. Hit GET /api/security/events
+4. Collect metrics</t>
+  </si>
+  <si>
+    <t>LOAD-119</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/events — Run 2</t>
+  </si>
+  <si>
+    <t>LOAD-120</t>
+  </si>
+  <si>
+    <t>Step Load (25→100 VUs) — GET /api/security/events — Run 3</t>
   </si>
   <si>
     <t>SAST-001</t>
@@ -3774,7 +4242,7 @@
     <t>BUG-001</t>
   </si>
   <si>
-    <t>Failure in "Empty credentials" — expected: Empty credentials should work correctly without errors</t>
+    <t>Failure in "User name displayed" — expected: User name displayed should work correctly without errors</t>
   </si>
   <si>
     <t>Open</t>
@@ -3783,25 +4251,25 @@
     <t>BUG-002</t>
   </si>
   <si>
-    <t>Failure in "Page title correct" — expected: Page title correct should work correctly without errors</t>
+    <t>Failure in "Event type badge" — expected: Event type badge should work correctly without errors</t>
   </si>
   <si>
     <t>BUG-003</t>
   </si>
   <si>
-    <t>Failure in "Login with email" — expected: Login with email should function correctly on mobile</t>
+    <t>Failure in "Animation at 60fps" — expected: Animation at 60fps should function correctly on mobile</t>
   </si>
   <si>
     <t>BUG-004</t>
   </si>
   <si>
-    <t>Failure in "SQL Injection Prevention" — expected: Parameterized queries prevent SQL injection</t>
+    <t>Failure in "XSS Prevention" — expected: Input is sanitized against XSS</t>
   </si>
   <si>
     <t>BUG-005</t>
   </si>
   <si>
-    <t>Failure in "POST /api/security/events - Error Leakage" — expected: No stack trace in error response</t>
+    <t>Failure in "Input Bounds Checking" — expected: Numeric inputs have min/max validation</t>
   </si>
   <si>
     <t>Total Tests</t>
@@ -4482,7 +4950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J261"/>
+  <dimension ref="A1:J321"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4651,13 +5119,13 @@
       <c r="I5" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>80</v>
+      <c r="J5" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>59</v>
@@ -4666,7 +5134,7 @@
         <v>60</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>62</v>
@@ -4675,13 +5143,13 @@
         <v>63</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>67</v>
@@ -4689,7 +5157,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -4698,7 +5166,7 @@
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
@@ -4707,10 +5175,10 @@
         <v>63</v>
       </c>
       <c r="G7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" t="s">
         <v>88</v>
-      </c>
-      <c r="H7" t="s">
-        <v>89</v>
       </c>
       <c r="I7" t="s">
         <v>66</v>
@@ -4721,7 +5189,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>59</v>
@@ -4730,7 +5198,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>62</v>
@@ -4739,10 +5207,10 @@
         <v>63</v>
       </c>
       <c r="G8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>66</v>
@@ -4753,7 +5221,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
         <v>59</v>
@@ -4762,7 +5230,7 @@
         <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>62</v>
@@ -4771,10 +5239,10 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" t="s">
         <v>96</v>
-      </c>
-      <c r="H9" t="s">
-        <v>97</v>
       </c>
       <c r="I9" t="s">
         <v>66</v>
@@ -4785,16 +5253,16 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>62</v>
@@ -4803,10 +5271,10 @@
         <v>63</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>66</v>
@@ -4817,16 +5285,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>62</v>
@@ -4835,13 +5303,13 @@
         <v>63</v>
       </c>
       <c r="G11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" t="s">
         <v>105</v>
       </c>
-      <c r="H11" t="s">
-        <v>106</v>
-      </c>
       <c r="I11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>67</v>
@@ -4849,16 +5317,16 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>62</v>
@@ -4867,13 +5335,13 @@
         <v>63</v>
       </c>
       <c r="G12" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="I12" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>67</v>
@@ -4881,16 +5349,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s">
         <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
         <v>62</v>
@@ -4899,10 +5367,10 @@
         <v>63</v>
       </c>
       <c r="G13" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" t="s">
         <v>113</v>
-      </c>
-      <c r="H13" t="s">
-        <v>114</v>
       </c>
       <c r="I13" t="s">
         <v>66</v>
@@ -4913,16 +5381,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>62</v>
@@ -4931,10 +5399,10 @@
         <v>63</v>
       </c>
       <c r="G14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>66</v>
@@ -4945,16 +5413,16 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
         <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
         <v>62</v>
@@ -4963,10 +5431,10 @@
         <v>63</v>
       </c>
       <c r="G15" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" t="s">
         <v>121</v>
-      </c>
-      <c r="H15" t="s">
-        <v>122</v>
       </c>
       <c r="I15" t="s">
         <v>66</v>
@@ -4977,16 +5445,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>62</v>
@@ -4995,10 +5463,10 @@
         <v>63</v>
       </c>
       <c r="G16" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>66</v>
@@ -5009,16 +5477,16 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B17" t="s">
         <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
         <v>62</v>
@@ -5027,10 +5495,10 @@
         <v>63</v>
       </c>
       <c r="G17" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" t="s">
         <v>129</v>
-      </c>
-      <c r="H17" t="s">
-        <v>130</v>
       </c>
       <c r="I17" t="s">
         <v>66</v>
@@ -5041,16 +5509,16 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>62</v>
@@ -5059,10 +5527,10 @@
         <v>63</v>
       </c>
       <c r="G18" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>66</v>
@@ -5073,16 +5541,16 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" t="s">
         <v>137</v>
-      </c>
-      <c r="B19" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" t="s">
-        <v>138</v>
       </c>
       <c r="E19" t="s">
         <v>62</v>
@@ -5091,10 +5559,10 @@
         <v>63</v>
       </c>
       <c r="G19" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" t="s">
         <v>139</v>
-      </c>
-      <c r="H19" t="s">
-        <v>140</v>
       </c>
       <c r="I19" t="s">
         <v>66</v>
@@ -5105,16 +5573,16 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>62</v>
@@ -5123,10 +5591,10 @@
         <v>63</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>66</v>
@@ -5137,16 +5605,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" t="s">
         <v>145</v>
-      </c>
-      <c r="B21" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" t="s">
-        <v>146</v>
       </c>
       <c r="E21" t="s">
         <v>62</v>
@@ -5155,10 +5623,10 @@
         <v>63</v>
       </c>
       <c r="G21" t="s">
+        <v>146</v>
+      </c>
+      <c r="H21" t="s">
         <v>147</v>
-      </c>
-      <c r="H21" t="s">
-        <v>148</v>
       </c>
       <c r="I21" t="s">
         <v>66</v>
@@ -5169,16 +5637,16 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>62</v>
@@ -5187,10 +5655,10 @@
         <v>63</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>66</v>
@@ -5201,16 +5669,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" t="s">
         <v>153</v>
-      </c>
-      <c r="B23" t="s">
-        <v>132</v>
-      </c>
-      <c r="C23" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" t="s">
-        <v>154</v>
       </c>
       <c r="E23" t="s">
         <v>62</v>
@@ -5219,10 +5687,10 @@
         <v>63</v>
       </c>
       <c r="G23" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" t="s">
         <v>155</v>
-      </c>
-      <c r="H23" t="s">
-        <v>156</v>
       </c>
       <c r="I23" t="s">
         <v>66</v>
@@ -5233,16 +5701,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>62</v>
@@ -5251,10 +5719,10 @@
         <v>63</v>
       </c>
       <c r="G24" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>66</v>
@@ -5265,16 +5733,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
         <v>161</v>
-      </c>
-      <c r="B25" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" t="s">
-        <v>133</v>
-      </c>
-      <c r="D25" t="s">
-        <v>162</v>
       </c>
       <c r="E25" t="s">
         <v>62</v>
@@ -5283,16 +5751,16 @@
         <v>63</v>
       </c>
       <c r="G25" t="s">
+        <v>162</v>
+      </c>
+      <c r="H25" t="s">
         <v>163</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="I25" t="s">
-        <v>66</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -5803,8 +6271,8 @@
       <c r="I41" t="s">
         <v>66</v>
       </c>
-      <c r="J41" s="6" t="s">
-        <v>67</v>
+      <c r="J41" s="7" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -6347,8 +6815,8 @@
       <c r="I58" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J58" s="8" t="s">
-        <v>80</v>
+      <c r="J58" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -7017,7 +7485,7 @@
         <v>395</v>
       </c>
       <c r="I79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J79" s="6" t="s">
         <v>67</v>
@@ -7051,8 +7519,8 @@
       <c r="I80" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J80" s="8" t="s">
-        <v>80</v>
+      <c r="J80" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -7081,7 +7549,7 @@
         <v>405</v>
       </c>
       <c r="I81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J81" s="6" t="s">
         <v>67</v>
@@ -7209,7 +7677,7 @@
         <v>421</v>
       </c>
       <c r="I85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J85" s="6" t="s">
         <v>67</v>
@@ -8841,7 +9309,7 @@
         <v>639</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J136" s="5" t="s">
         <v>67</v>
@@ -9003,8 +9471,8 @@
       <c r="I141" t="s">
         <v>66</v>
       </c>
-      <c r="J141" s="6" t="s">
-        <v>67</v>
+      <c r="J141" s="7" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -9993,7 +10461,7 @@
         <v>667</v>
       </c>
       <c r="I172" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J172" s="5" t="s">
         <v>67</v>
@@ -10025,7 +10493,7 @@
         <v>667</v>
       </c>
       <c r="I173" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J173" s="6" t="s">
         <v>67</v>
@@ -10057,7 +10525,7 @@
         <v>667</v>
       </c>
       <c r="I174" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J174" s="5" t="s">
         <v>67</v>
@@ -10089,7 +10557,7 @@
         <v>667</v>
       </c>
       <c r="I175" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J175" s="6" t="s">
         <v>67</v>
@@ -10121,7 +10589,7 @@
         <v>667</v>
       </c>
       <c r="I176" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J176" s="5" t="s">
         <v>67</v>
@@ -10153,7 +10621,7 @@
         <v>667</v>
       </c>
       <c r="I177" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J177" s="6" t="s">
         <v>67</v>
@@ -10185,7 +10653,7 @@
         <v>667</v>
       </c>
       <c r="I178" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J178" s="5" t="s">
         <v>67</v>
@@ -10217,7 +10685,7 @@
         <v>667</v>
       </c>
       <c r="I179" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J179" s="6" t="s">
         <v>67</v>
@@ -10249,7 +10717,7 @@
         <v>667</v>
       </c>
       <c r="I180" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J180" s="5" t="s">
         <v>67</v>
@@ -10281,7 +10749,7 @@
         <v>667</v>
       </c>
       <c r="I181" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J181" s="6" t="s">
         <v>67</v>
@@ -10313,7 +10781,7 @@
         <v>667</v>
       </c>
       <c r="I182" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J182" s="5" t="s">
         <v>67</v>
@@ -10345,7 +10813,7 @@
         <v>667</v>
       </c>
       <c r="I183" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J183" s="6" t="s">
         <v>67</v>
@@ -10377,7 +10845,7 @@
         <v>667</v>
       </c>
       <c r="I184" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J184" s="5" t="s">
         <v>67</v>
@@ -10409,7 +10877,7 @@
         <v>667</v>
       </c>
       <c r="I185" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J185" s="6" t="s">
         <v>67</v>
@@ -10441,7 +10909,7 @@
         <v>667</v>
       </c>
       <c r="I186" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J186" s="5" t="s">
         <v>67</v>
@@ -10932,28 +11400,28 @@
         <v>810</v>
       </c>
       <c r="B202" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C202" s="4" t="s">
+      <c r="D202" s="4" t="s">
         <v>812</v>
       </c>
-      <c r="D202" s="4" t="s">
+      <c r="E202" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F202" s="4" t="s">
         <v>813</v>
       </c>
-      <c r="E202" s="4" t="s">
+      <c r="G202" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="F202" s="4" t="s">
-        <v>815</v>
-      </c>
-      <c r="G202" s="4" t="s">
-        <v>816</v>
-      </c>
       <c r="H202" s="4" t="s">
-        <v>817</v>
+        <v>667</v>
       </c>
       <c r="I202" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J202" s="5" t="s">
         <v>67</v>
@@ -10961,31 +11429,31 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B203" t="s">
+        <v>661</v>
+      </c>
+      <c r="C203" t="s">
         <v>811</v>
       </c>
-      <c r="C203" t="s">
-        <v>812</v>
-      </c>
       <c r="D203" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="E203" t="s">
+        <v>664</v>
+      </c>
+      <c r="F203" t="s">
+        <v>813</v>
+      </c>
+      <c r="G203" t="s">
         <v>814</v>
       </c>
-      <c r="F203" t="s">
-        <v>815</v>
-      </c>
-      <c r="G203" t="s">
-        <v>820</v>
-      </c>
       <c r="H203" t="s">
-        <v>821</v>
+        <v>667</v>
       </c>
       <c r="I203" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J203" s="6" t="s">
         <v>67</v>
@@ -10993,31 +11461,31 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="B204" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C204" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C204" s="4" t="s">
-        <v>812</v>
-      </c>
       <c r="D204" s="4" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="E204" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="G204" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="F204" s="4" t="s">
-        <v>815</v>
-      </c>
-      <c r="G204" s="4" t="s">
-        <v>824</v>
-      </c>
       <c r="H204" s="4" t="s">
-        <v>825</v>
+        <v>667</v>
       </c>
       <c r="I204" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J204" s="5" t="s">
         <v>67</v>
@@ -11025,31 +11493,31 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="B205" t="s">
+        <v>661</v>
+      </c>
+      <c r="C205" t="s">
         <v>811</v>
       </c>
-      <c r="C205" t="s">
-        <v>812</v>
-      </c>
       <c r="D205" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="E205" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F205" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G205" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="H205" t="s">
-        <v>829</v>
+        <v>667</v>
       </c>
       <c r="I205" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J205" s="6" t="s">
         <v>67</v>
@@ -11057,28 +11525,28 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="B206" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C206" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C206" s="4" t="s">
-        <v>812</v>
-      </c>
       <c r="D206" s="4" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>833</v>
+        <v>667</v>
       </c>
       <c r="I206" s="4" t="s">
         <v>66</v>
@@ -11089,60 +11557,60 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="B207" t="s">
+        <v>661</v>
+      </c>
+      <c r="C207" t="s">
         <v>811</v>
       </c>
-      <c r="C207" t="s">
-        <v>835</v>
-      </c>
       <c r="D207" t="s">
-        <v>836</v>
+        <v>825</v>
       </c>
       <c r="E207" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F207" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G207" t="s">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="H207" t="s">
-        <v>838</v>
+        <v>667</v>
       </c>
       <c r="I207" t="s">
-        <v>85</v>
-      </c>
-      <c r="J207" s="7" t="s">
-        <v>80</v>
+        <v>66</v>
+      </c>
+      <c r="J207" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="B208" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C208" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C208" s="4" t="s">
-        <v>835</v>
-      </c>
       <c r="D208" s="4" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>842</v>
+        <v>667</v>
       </c>
       <c r="I208" s="4" t="s">
         <v>66</v>
@@ -11153,31 +11621,31 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>843</v>
+        <v>829</v>
       </c>
       <c r="B209" t="s">
+        <v>661</v>
+      </c>
+      <c r="C209" t="s">
         <v>811</v>
       </c>
-      <c r="C209" t="s">
-        <v>835</v>
-      </c>
       <c r="D209" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="E209" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F209" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G209" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
       <c r="H209" t="s">
-        <v>846</v>
+        <v>667</v>
       </c>
       <c r="I209" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J209" s="6" t="s">
         <v>67</v>
@@ -11185,28 +11653,28 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="B210" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C210" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C210" s="4" t="s">
-        <v>835</v>
-      </c>
       <c r="D210" s="4" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>849</v>
+        <v>828</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>850</v>
+        <v>667</v>
       </c>
       <c r="I210" s="4" t="s">
         <v>66</v>
@@ -11217,28 +11685,28 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>851</v>
+        <v>833</v>
       </c>
       <c r="B211" t="s">
+        <v>661</v>
+      </c>
+      <c r="C211" t="s">
         <v>811</v>
       </c>
-      <c r="C211" t="s">
+      <c r="D211" t="s">
+        <v>834</v>
+      </c>
+      <c r="E211" t="s">
+        <v>664</v>
+      </c>
+      <c r="F211" t="s">
+        <v>813</v>
+      </c>
+      <c r="G211" t="s">
         <v>835</v>
       </c>
-      <c r="D211" t="s">
-        <v>852</v>
-      </c>
-      <c r="E211" t="s">
-        <v>814</v>
-      </c>
-      <c r="F211" t="s">
-        <v>815</v>
-      </c>
-      <c r="G211" t="s">
-        <v>853</v>
-      </c>
       <c r="H211" t="s">
-        <v>854</v>
+        <v>667</v>
       </c>
       <c r="I211" t="s">
         <v>66</v>
@@ -11249,28 +11717,28 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="B212" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C212" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C212" s="4" t="s">
-        <v>856</v>
-      </c>
       <c r="D212" s="4" t="s">
-        <v>857</v>
+        <v>837</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
       <c r="H212" s="4" t="s">
-        <v>859</v>
+        <v>667</v>
       </c>
       <c r="I212" s="4" t="s">
         <v>66</v>
@@ -11281,28 +11749,28 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>860</v>
+        <v>838</v>
       </c>
       <c r="B213" t="s">
+        <v>661</v>
+      </c>
+      <c r="C213" t="s">
         <v>811</v>
       </c>
-      <c r="C213" t="s">
-        <v>856</v>
-      </c>
       <c r="D213" t="s">
-        <v>861</v>
+        <v>839</v>
       </c>
       <c r="E213" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F213" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G213" t="s">
-        <v>862</v>
+        <v>835</v>
       </c>
       <c r="H213" t="s">
-        <v>863</v>
+        <v>667</v>
       </c>
       <c r="I213" t="s">
         <v>66</v>
@@ -11313,28 +11781,28 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>864</v>
+        <v>840</v>
       </c>
       <c r="B214" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C214" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C214" s="4" t="s">
-        <v>856</v>
-      </c>
       <c r="D214" s="4" t="s">
-        <v>865</v>
+        <v>841</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G214" s="4" t="s">
-        <v>866</v>
+        <v>842</v>
       </c>
       <c r="H214" s="4" t="s">
-        <v>867</v>
+        <v>667</v>
       </c>
       <c r="I214" s="4" t="s">
         <v>66</v>
@@ -11345,28 +11813,28 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>868</v>
+        <v>843</v>
       </c>
       <c r="B215" t="s">
+        <v>661</v>
+      </c>
+      <c r="C215" t="s">
         <v>811</v>
       </c>
-      <c r="C215" t="s">
-        <v>869</v>
-      </c>
       <c r="D215" t="s">
-        <v>870</v>
+        <v>844</v>
       </c>
       <c r="E215" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F215" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G215" t="s">
-        <v>871</v>
+        <v>842</v>
       </c>
       <c r="H215" t="s">
-        <v>872</v>
+        <v>667</v>
       </c>
       <c r="I215" t="s">
         <v>66</v>
@@ -11377,28 +11845,28 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>873</v>
+        <v>845</v>
       </c>
       <c r="B216" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C216" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C216" s="4" t="s">
-        <v>869</v>
-      </c>
       <c r="D216" s="4" t="s">
-        <v>874</v>
+        <v>846</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G216" s="4" t="s">
-        <v>875</v>
+        <v>842</v>
       </c>
       <c r="H216" s="4" t="s">
-        <v>876</v>
+        <v>667</v>
       </c>
       <c r="I216" s="4" t="s">
         <v>66</v>
@@ -11409,28 +11877,28 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>877</v>
+        <v>847</v>
       </c>
       <c r="B217" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C217" t="s">
-        <v>869</v>
+        <v>848</v>
       </c>
       <c r="D217" t="s">
-        <v>878</v>
+        <v>849</v>
       </c>
       <c r="E217" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F217" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G217" t="s">
-        <v>879</v>
+        <v>851</v>
       </c>
       <c r="H217" t="s">
-        <v>880</v>
+        <v>667</v>
       </c>
       <c r="I217" t="s">
         <v>66</v>
@@ -11441,28 +11909,28 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>881</v>
+        <v>852</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>869</v>
+        <v>848</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>882</v>
+        <v>853</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>883</v>
+        <v>851</v>
       </c>
       <c r="H218" s="4" t="s">
-        <v>884</v>
+        <v>667</v>
       </c>
       <c r="I218" s="4" t="s">
         <v>66</v>
@@ -11473,31 +11941,31 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>885</v>
+        <v>854</v>
       </c>
       <c r="B219" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C219" t="s">
-        <v>886</v>
+        <v>848</v>
       </c>
       <c r="D219" t="s">
-        <v>887</v>
+        <v>855</v>
       </c>
       <c r="E219" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F219" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G219" t="s">
-        <v>888</v>
+        <v>851</v>
       </c>
       <c r="H219" t="s">
-        <v>889</v>
+        <v>667</v>
       </c>
       <c r="I219" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J219" s="6" t="s">
         <v>67</v>
@@ -11505,28 +11973,28 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>886</v>
+        <v>848</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>891</v>
+        <v>857</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G220" s="4" t="s">
-        <v>892</v>
+        <v>858</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>893</v>
+        <v>667</v>
       </c>
       <c r="I220" s="4" t="s">
         <v>66</v>
@@ -11537,28 +12005,28 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>894</v>
+        <v>859</v>
       </c>
       <c r="B221" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C221" t="s">
-        <v>886</v>
+        <v>848</v>
       </c>
       <c r="D221" t="s">
-        <v>895</v>
+        <v>860</v>
       </c>
       <c r="E221" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F221" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G221" t="s">
-        <v>896</v>
+        <v>858</v>
       </c>
       <c r="H221" t="s">
-        <v>897</v>
+        <v>667</v>
       </c>
       <c r="I221" t="s">
         <v>66</v>
@@ -11569,28 +12037,28 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>898</v>
+        <v>861</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>899</v>
+        <v>848</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>900</v>
+        <v>862</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>901</v>
+        <v>858</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>902</v>
+        <v>667</v>
       </c>
       <c r="I222" s="4" t="s">
         <v>66</v>
@@ -11601,28 +12069,28 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>903</v>
+        <v>863</v>
       </c>
       <c r="B223" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C223" t="s">
-        <v>899</v>
+        <v>848</v>
       </c>
       <c r="D223" t="s">
-        <v>904</v>
+        <v>864</v>
       </c>
       <c r="E223" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F223" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G223" t="s">
-        <v>905</v>
+        <v>865</v>
       </c>
       <c r="H223" t="s">
-        <v>906</v>
+        <v>667</v>
       </c>
       <c r="I223" t="s">
         <v>66</v>
@@ -11633,28 +12101,28 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>907</v>
+        <v>866</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>908</v>
+        <v>848</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>909</v>
+        <v>867</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>910</v>
+        <v>865</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>911</v>
+        <v>667</v>
       </c>
       <c r="I224" s="4" t="s">
         <v>66</v>
@@ -11665,28 +12133,28 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>912</v>
+        <v>868</v>
       </c>
       <c r="B225" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C225" t="s">
-        <v>908</v>
+        <v>848</v>
       </c>
       <c r="D225" t="s">
-        <v>913</v>
+        <v>869</v>
       </c>
       <c r="E225" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F225" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G225" t="s">
-        <v>914</v>
+        <v>865</v>
       </c>
       <c r="H225" t="s">
-        <v>915</v>
+        <v>667</v>
       </c>
       <c r="I225" t="s">
         <v>66</v>
@@ -11697,31 +12165,31 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>916</v>
+        <v>870</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>917</v>
+        <v>848</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>918</v>
+        <v>871</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>919</v>
+        <v>872</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>920</v>
+        <v>667</v>
       </c>
       <c r="I226" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J226" s="5" t="s">
         <v>67</v>
@@ -11729,28 +12197,28 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>921</v>
+        <v>873</v>
       </c>
       <c r="B227" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C227" t="s">
-        <v>917</v>
+        <v>848</v>
       </c>
       <c r="D227" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="E227" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F227" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G227" t="s">
-        <v>923</v>
+        <v>872</v>
       </c>
       <c r="H227" t="s">
-        <v>924</v>
+        <v>667</v>
       </c>
       <c r="I227" t="s">
         <v>66</v>
@@ -11761,28 +12229,28 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>925</v>
+        <v>875</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>926</v>
+        <v>848</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>927</v>
+        <v>876</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G228" s="4" t="s">
-        <v>928</v>
+        <v>872</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>929</v>
+        <v>667</v>
       </c>
       <c r="I228" s="4" t="s">
         <v>66</v>
@@ -11793,28 +12261,28 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>930</v>
+        <v>877</v>
       </c>
       <c r="B229" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C229" t="s">
-        <v>926</v>
+        <v>848</v>
       </c>
       <c r="D229" t="s">
-        <v>931</v>
+        <v>878</v>
       </c>
       <c r="E229" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F229" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G229" t="s">
-        <v>932</v>
+        <v>879</v>
       </c>
       <c r="H229" t="s">
-        <v>933</v>
+        <v>667</v>
       </c>
       <c r="I229" t="s">
         <v>66</v>
@@ -11825,28 +12293,28 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>934</v>
+        <v>880</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>926</v>
+        <v>848</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>935</v>
+        <v>881</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>936</v>
+        <v>879</v>
       </c>
       <c r="H230" s="4" t="s">
-        <v>937</v>
+        <v>667</v>
       </c>
       <c r="I230" s="4" t="s">
         <v>66</v>
@@ -11857,28 +12325,28 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>938</v>
+        <v>882</v>
       </c>
       <c r="B231" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C231" t="s">
-        <v>926</v>
+        <v>848</v>
       </c>
       <c r="D231" t="s">
-        <v>939</v>
+        <v>883</v>
       </c>
       <c r="E231" t="s">
-        <v>814</v>
+        <v>664</v>
       </c>
       <c r="F231" t="s">
-        <v>815</v>
+        <v>850</v>
       </c>
       <c r="G231" t="s">
-        <v>940</v>
+        <v>879</v>
       </c>
       <c r="H231" t="s">
-        <v>941</v>
+        <v>667</v>
       </c>
       <c r="I231" t="s">
         <v>66</v>
@@ -11889,28 +12357,28 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>942</v>
+        <v>884</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>812</v>
+        <v>885</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>944</v>
+        <v>886</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>947</v>
+        <v>666</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>948</v>
+        <v>667</v>
       </c>
       <c r="I232" s="4" t="s">
         <v>66</v>
@@ -11921,28 +12389,28 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>949</v>
+        <v>887</v>
       </c>
       <c r="B233" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C233" t="s">
-        <v>812</v>
+        <v>885</v>
       </c>
       <c r="D233" t="s">
-        <v>950</v>
+        <v>888</v>
       </c>
       <c r="E233" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F233" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G233" t="s">
-        <v>951</v>
+        <v>666</v>
       </c>
       <c r="H233" t="s">
-        <v>952</v>
+        <v>667</v>
       </c>
       <c r="I233" t="s">
         <v>66</v>
@@ -11953,31 +12421,31 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>953</v>
+        <v>889</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>812</v>
+        <v>885</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>954</v>
+        <v>890</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>955</v>
+        <v>666</v>
       </c>
       <c r="H234" s="4" t="s">
-        <v>956</v>
+        <v>667</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J234" s="5" t="s">
         <v>67</v>
@@ -11985,28 +12453,28 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>957</v>
+        <v>891</v>
       </c>
       <c r="B235" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C235" t="s">
-        <v>812</v>
+        <v>885</v>
       </c>
       <c r="D235" t="s">
-        <v>958</v>
+        <v>892</v>
       </c>
       <c r="E235" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F235" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G235" t="s">
-        <v>959</v>
+        <v>674</v>
       </c>
       <c r="H235" t="s">
-        <v>960</v>
+        <v>667</v>
       </c>
       <c r="I235" t="s">
         <v>66</v>
@@ -12017,31 +12485,31 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>961</v>
+        <v>893</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>856</v>
+        <v>885</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>962</v>
+        <v>894</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>963</v>
+        <v>674</v>
       </c>
       <c r="H236" s="4" t="s">
-        <v>964</v>
+        <v>667</v>
       </c>
       <c r="I236" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J236" s="5" t="s">
         <v>67</v>
@@ -12049,28 +12517,28 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>965</v>
+        <v>895</v>
       </c>
       <c r="B237" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C237" t="s">
-        <v>856</v>
+        <v>885</v>
       </c>
       <c r="D237" t="s">
-        <v>966</v>
+        <v>896</v>
       </c>
       <c r="E237" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F237" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G237" t="s">
-        <v>967</v>
+        <v>674</v>
       </c>
       <c r="H237" t="s">
-        <v>968</v>
+        <v>667</v>
       </c>
       <c r="I237" t="s">
         <v>66</v>
@@ -12081,31 +12549,31 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>969</v>
+        <v>897</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>970</v>
+        <v>885</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>971</v>
+        <v>898</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>972</v>
+        <v>681</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>973</v>
+        <v>667</v>
       </c>
       <c r="I238" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J238" s="5" t="s">
         <v>67</v>
@@ -12113,31 +12581,31 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>974</v>
+        <v>899</v>
       </c>
       <c r="B239" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C239" t="s">
-        <v>970</v>
+        <v>885</v>
       </c>
       <c r="D239" t="s">
-        <v>975</v>
+        <v>900</v>
       </c>
       <c r="E239" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F239" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G239" t="s">
-        <v>976</v>
+        <v>681</v>
       </c>
       <c r="H239" t="s">
-        <v>977</v>
+        <v>667</v>
       </c>
       <c r="I239" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J239" s="6" t="s">
         <v>67</v>
@@ -12145,28 +12613,28 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>978</v>
+        <v>901</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>970</v>
+        <v>885</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>979</v>
+        <v>902</v>
       </c>
       <c r="E240" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>980</v>
+        <v>681</v>
       </c>
       <c r="H240" s="4" t="s">
-        <v>981</v>
+        <v>667</v>
       </c>
       <c r="I240" s="4" t="s">
         <v>66</v>
@@ -12177,31 +12645,31 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>982</v>
+        <v>903</v>
       </c>
       <c r="B241" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C241" t="s">
-        <v>983</v>
+        <v>885</v>
       </c>
       <c r="D241" t="s">
-        <v>984</v>
+        <v>904</v>
       </c>
       <c r="E241" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F241" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G241" t="s">
-        <v>985</v>
+        <v>688</v>
       </c>
       <c r="H241" t="s">
-        <v>986</v>
+        <v>667</v>
       </c>
       <c r="I241" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J241" s="6" t="s">
         <v>67</v>
@@ -12209,28 +12677,28 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>987</v>
+        <v>905</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>983</v>
+        <v>885</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>988</v>
+        <v>906</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>989</v>
+        <v>688</v>
       </c>
       <c r="H242" s="4" t="s">
-        <v>990</v>
+        <v>667</v>
       </c>
       <c r="I242" s="4" t="s">
         <v>66</v>
@@ -12241,28 +12709,28 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>991</v>
+        <v>907</v>
       </c>
       <c r="B243" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C243" t="s">
-        <v>992</v>
+        <v>885</v>
       </c>
       <c r="D243" t="s">
-        <v>993</v>
+        <v>908</v>
       </c>
       <c r="E243" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F243" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G243" t="s">
-        <v>994</v>
+        <v>688</v>
       </c>
       <c r="H243" t="s">
-        <v>995</v>
+        <v>667</v>
       </c>
       <c r="I243" t="s">
         <v>66</v>
@@ -12273,28 +12741,28 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
-        <v>996</v>
+        <v>909</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>992</v>
+        <v>885</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>997</v>
+        <v>910</v>
       </c>
       <c r="E244" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G244" s="4" t="s">
-        <v>998</v>
+        <v>695</v>
       </c>
       <c r="H244" s="4" t="s">
-        <v>999</v>
+        <v>667</v>
       </c>
       <c r="I244" s="4" t="s">
         <v>66</v>
@@ -12305,28 +12773,28 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1000</v>
+        <v>911</v>
       </c>
       <c r="B245" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C245" t="s">
-        <v>992</v>
+        <v>885</v>
       </c>
       <c r="D245" t="s">
-        <v>1001</v>
+        <v>912</v>
       </c>
       <c r="E245" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F245" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G245" t="s">
-        <v>1002</v>
+        <v>695</v>
       </c>
       <c r="H245" t="s">
-        <v>1003</v>
+        <v>667</v>
       </c>
       <c r="I245" t="s">
         <v>66</v>
@@ -12337,63 +12805,63 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
-        <v>1004</v>
+        <v>913</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>992</v>
+        <v>885</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>1005</v>
+        <v>914</v>
       </c>
       <c r="E246" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G246" s="4" t="s">
-        <v>1006</v>
+        <v>695</v>
       </c>
       <c r="H246" s="4" t="s">
-        <v>1007</v>
+        <v>667</v>
       </c>
       <c r="I246" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J246" s="8" t="s">
-        <v>80</v>
+      <c r="J246" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1008</v>
+        <v>915</v>
       </c>
       <c r="B247" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C247" t="s">
-        <v>1009</v>
+        <v>916</v>
       </c>
       <c r="D247" t="s">
-        <v>1010</v>
+        <v>917</v>
       </c>
       <c r="E247" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F247" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G247" t="s">
-        <v>1011</v>
+        <v>918</v>
       </c>
       <c r="H247" t="s">
-        <v>1012</v>
+        <v>667</v>
       </c>
       <c r="I247" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J247" s="6" t="s">
         <v>67</v>
@@ -12401,31 +12869,31 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
-        <v>1013</v>
+        <v>919</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>1009</v>
+        <v>916</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>1014</v>
+        <v>920</v>
       </c>
       <c r="E248" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G248" s="4" t="s">
-        <v>1015</v>
+        <v>918</v>
       </c>
       <c r="H248" s="4" t="s">
-        <v>1016</v>
+        <v>667</v>
       </c>
       <c r="I248" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J248" s="5" t="s">
         <v>67</v>
@@ -12433,31 +12901,31 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1017</v>
+        <v>921</v>
       </c>
       <c r="B249" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C249" t="s">
-        <v>1009</v>
+        <v>916</v>
       </c>
       <c r="D249" t="s">
-        <v>1018</v>
+        <v>922</v>
       </c>
       <c r="E249" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F249" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G249" t="s">
-        <v>1019</v>
+        <v>918</v>
       </c>
       <c r="H249" t="s">
-        <v>1020</v>
+        <v>667</v>
       </c>
       <c r="I249" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J249" s="6" t="s">
         <v>67</v>
@@ -12465,31 +12933,31 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
-        <v>1021</v>
+        <v>923</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>1009</v>
+        <v>916</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>1022</v>
+        <v>924</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G250" s="4" t="s">
-        <v>1023</v>
+        <v>925</v>
       </c>
       <c r="H250" s="4" t="s">
-        <v>1024</v>
+        <v>667</v>
       </c>
       <c r="I250" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J250" s="5" t="s">
         <v>67</v>
@@ -12497,31 +12965,31 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1025</v>
+        <v>926</v>
       </c>
       <c r="B251" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C251" t="s">
-        <v>1009</v>
+        <v>916</v>
       </c>
       <c r="D251" t="s">
-        <v>1026</v>
+        <v>927</v>
       </c>
       <c r="E251" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F251" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G251" t="s">
-        <v>1027</v>
+        <v>925</v>
       </c>
       <c r="H251" t="s">
-        <v>1028</v>
+        <v>667</v>
       </c>
       <c r="I251" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J251" s="6" t="s">
         <v>67</v>
@@ -12529,28 +12997,28 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>1029</v>
+        <v>928</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>1030</v>
+        <v>916</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>852</v>
+        <v>929</v>
       </c>
       <c r="E252" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>1031</v>
+        <v>925</v>
       </c>
       <c r="H252" s="4" t="s">
-        <v>1032</v>
+        <v>667</v>
       </c>
       <c r="I252" s="4" t="s">
         <v>66</v>
@@ -12561,28 +13029,28 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1033</v>
+        <v>930</v>
       </c>
       <c r="B253" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C253" t="s">
-        <v>1030</v>
+        <v>916</v>
       </c>
       <c r="D253" t="s">
-        <v>1034</v>
+        <v>931</v>
       </c>
       <c r="E253" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F253" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G253" t="s">
-        <v>1035</v>
+        <v>932</v>
       </c>
       <c r="H253" t="s">
-        <v>1036</v>
+        <v>667</v>
       </c>
       <c r="I253" t="s">
         <v>66</v>
@@ -12593,28 +13061,28 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>1037</v>
+        <v>933</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>1030</v>
+        <v>916</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>1038</v>
+        <v>934</v>
       </c>
       <c r="E254" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G254" s="4" t="s">
-        <v>1039</v>
+        <v>932</v>
       </c>
       <c r="H254" s="4" t="s">
-        <v>1040</v>
+        <v>667</v>
       </c>
       <c r="I254" s="4" t="s">
         <v>66</v>
@@ -12625,28 +13093,28 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1041</v>
+        <v>935</v>
       </c>
       <c r="B255" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C255" t="s">
-        <v>1042</v>
+        <v>916</v>
       </c>
       <c r="D255" t="s">
-        <v>1043</v>
+        <v>936</v>
       </c>
       <c r="E255" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F255" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G255" t="s">
-        <v>1044</v>
+        <v>932</v>
       </c>
       <c r="H255" t="s">
-        <v>1045</v>
+        <v>667</v>
       </c>
       <c r="I255" t="s">
         <v>66</v>
@@ -12657,28 +13125,28 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>1046</v>
+        <v>937</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>1042</v>
+        <v>916</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>1047</v>
+        <v>938</v>
       </c>
       <c r="E256" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>1048</v>
+        <v>939</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>1049</v>
+        <v>667</v>
       </c>
       <c r="I256" s="4" t="s">
         <v>66</v>
@@ -12689,31 +13157,31 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1050</v>
+        <v>940</v>
       </c>
       <c r="B257" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C257" t="s">
-        <v>1051</v>
+        <v>916</v>
       </c>
       <c r="D257" t="s">
-        <v>1052</v>
+        <v>941</v>
       </c>
       <c r="E257" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F257" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G257" t="s">
-        <v>1053</v>
+        <v>939</v>
       </c>
       <c r="H257" t="s">
-        <v>1054</v>
+        <v>667</v>
       </c>
       <c r="I257" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J257" s="6" t="s">
         <v>67</v>
@@ -12721,31 +13189,31 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>1055</v>
+        <v>942</v>
       </c>
       <c r="B258" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D258" s="4" t="s">
         <v>943</v>
       </c>
-      <c r="C258" s="4" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D258" s="4" t="s">
-        <v>1056</v>
-      </c>
       <c r="E258" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>946</v>
+        <v>665</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>1057</v>
+        <v>939</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>1058</v>
+        <v>667</v>
       </c>
       <c r="I258" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J258" s="5" t="s">
         <v>67</v>
@@ -12753,28 +13221,28 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1059</v>
+        <v>944</v>
       </c>
       <c r="B259" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C259" t="s">
-        <v>926</v>
+        <v>916</v>
       </c>
       <c r="D259" t="s">
-        <v>1060</v>
+        <v>945</v>
       </c>
       <c r="E259" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F259" t="s">
+        <v>665</v>
+      </c>
+      <c r="G259" t="s">
         <v>946</v>
       </c>
-      <c r="G259" t="s">
-        <v>1061</v>
-      </c>
       <c r="H259" t="s">
-        <v>1062</v>
+        <v>667</v>
       </c>
       <c r="I259" t="s">
         <v>66</v>
@@ -12785,28 +13253,28 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>1063</v>
+        <v>947</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>943</v>
+        <v>661</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>926</v>
+        <v>916</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>1064</v>
+        <v>948</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>945</v>
+        <v>664</v>
       </c>
       <c r="F260" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="G260" s="4" t="s">
         <v>946</v>
       </c>
-      <c r="G260" s="4" t="s">
-        <v>1065</v>
-      </c>
       <c r="H260" s="4" t="s">
-        <v>1066</v>
+        <v>667</v>
       </c>
       <c r="I260" s="4" t="s">
         <v>66</v>
@@ -12817,33 +13285,1953 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>949</v>
+      </c>
+      <c r="B261" t="s">
+        <v>661</v>
+      </c>
+      <c r="C261" t="s">
+        <v>916</v>
+      </c>
+      <c r="D261" t="s">
+        <v>950</v>
+      </c>
+      <c r="E261" t="s">
+        <v>664</v>
+      </c>
+      <c r="F261" t="s">
+        <v>665</v>
+      </c>
+      <c r="G261" t="s">
+        <v>946</v>
+      </c>
+      <c r="H261" t="s">
+        <v>667</v>
+      </c>
+      <c r="I261" t="s">
+        <v>66</v>
+      </c>
+      <c r="J261" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="E262" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G262" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="H262" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="I262" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J262" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>959</v>
+      </c>
+      <c r="B263" t="s">
+        <v>952</v>
+      </c>
+      <c r="C263" t="s">
+        <v>953</v>
+      </c>
+      <c r="D263" t="s">
+        <v>960</v>
+      </c>
+      <c r="E263" t="s">
+        <v>955</v>
+      </c>
+      <c r="F263" t="s">
+        <v>956</v>
+      </c>
+      <c r="G263" t="s">
+        <v>961</v>
+      </c>
+      <c r="H263" t="s">
+        <v>962</v>
+      </c>
+      <c r="I263" t="s">
+        <v>84</v>
+      </c>
+      <c r="J263" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="E264" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G264" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="H264" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="I264" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J264" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>967</v>
+      </c>
+      <c r="B265" t="s">
+        <v>952</v>
+      </c>
+      <c r="C265" t="s">
+        <v>953</v>
+      </c>
+      <c r="D265" t="s">
+        <v>968</v>
+      </c>
+      <c r="E265" t="s">
+        <v>955</v>
+      </c>
+      <c r="F265" t="s">
+        <v>956</v>
+      </c>
+      <c r="G265" t="s">
+        <v>969</v>
+      </c>
+      <c r="H265" t="s">
+        <v>970</v>
+      </c>
+      <c r="I265" t="s">
+        <v>84</v>
+      </c>
+      <c r="J265" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="E266" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G266" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="H266" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="I266" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J266" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>975</v>
+      </c>
+      <c r="B267" t="s">
+        <v>952</v>
+      </c>
+      <c r="C267" t="s">
+        <v>976</v>
+      </c>
+      <c r="D267" t="s">
+        <v>977</v>
+      </c>
+      <c r="E267" t="s">
+        <v>955</v>
+      </c>
+      <c r="F267" t="s">
+        <v>956</v>
+      </c>
+      <c r="G267" t="s">
+        <v>978</v>
+      </c>
+      <c r="H267" t="s">
+        <v>979</v>
+      </c>
+      <c r="I267" t="s">
+        <v>84</v>
+      </c>
+      <c r="J267" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="E268" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G268" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="H268" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="I268" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J268" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>984</v>
+      </c>
+      <c r="B269" t="s">
+        <v>952</v>
+      </c>
+      <c r="C269" t="s">
+        <v>976</v>
+      </c>
+      <c r="D269" t="s">
+        <v>985</v>
+      </c>
+      <c r="E269" t="s">
+        <v>955</v>
+      </c>
+      <c r="F269" t="s">
+        <v>956</v>
+      </c>
+      <c r="G269" t="s">
+        <v>986</v>
+      </c>
+      <c r="H269" t="s">
+        <v>987</v>
+      </c>
+      <c r="I269" t="s">
+        <v>84</v>
+      </c>
+      <c r="J269" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="E270" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G270" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="H270" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="I270" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J270" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>992</v>
+      </c>
+      <c r="B271" t="s">
+        <v>952</v>
+      </c>
+      <c r="C271" t="s">
+        <v>976</v>
+      </c>
+      <c r="D271" t="s">
+        <v>993</v>
+      </c>
+      <c r="E271" t="s">
+        <v>955</v>
+      </c>
+      <c r="F271" t="s">
+        <v>956</v>
+      </c>
+      <c r="G271" t="s">
+        <v>994</v>
+      </c>
+      <c r="H271" t="s">
+        <v>995</v>
+      </c>
+      <c r="I271" t="s">
+        <v>66</v>
+      </c>
+      <c r="J271" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="E272" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G272" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="H272" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I272" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J272" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B273" t="s">
+        <v>952</v>
+      </c>
+      <c r="C273" t="s">
+        <v>997</v>
+      </c>
+      <c r="D273" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E273" t="s">
+        <v>955</v>
+      </c>
+      <c r="F273" t="s">
+        <v>956</v>
+      </c>
+      <c r="G273" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H273" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I273" t="s">
+        <v>66</v>
+      </c>
+      <c r="J273" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E274" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G274" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H274" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I274" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J274" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B275" t="s">
+        <v>952</v>
+      </c>
+      <c r="C275" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D275" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E275" t="s">
+        <v>955</v>
+      </c>
+      <c r="F275" t="s">
+        <v>956</v>
+      </c>
+      <c r="G275" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H275" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I275" t="s">
+        <v>66</v>
+      </c>
+      <c r="J275" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B276" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D276" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E276" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G276" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H276" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I276" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J276" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B277" t="s">
+        <v>952</v>
+      </c>
+      <c r="C277" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D277" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E277" t="s">
+        <v>955</v>
+      </c>
+      <c r="F277" t="s">
+        <v>956</v>
+      </c>
+      <c r="G277" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H277" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I277" t="s">
+        <v>66</v>
+      </c>
+      <c r="J277" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B278" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D278" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E278" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G278" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H278" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I278" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J278" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B279" t="s">
+        <v>952</v>
+      </c>
+      <c r="C279" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E279" t="s">
+        <v>955</v>
+      </c>
+      <c r="F279" t="s">
+        <v>956</v>
+      </c>
+      <c r="G279" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H279" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I279" t="s">
+        <v>84</v>
+      </c>
+      <c r="J279" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A280" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B280" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D280" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E280" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G280" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H280" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I280" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J280" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B281" t="s">
+        <v>952</v>
+      </c>
+      <c r="C281" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E281" t="s">
+        <v>955</v>
+      </c>
+      <c r="F281" t="s">
+        <v>956</v>
+      </c>
+      <c r="G281" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H281" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I281" t="s">
+        <v>66</v>
+      </c>
+      <c r="J281" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B282" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D282" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E282" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F282" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G282" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H282" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I282" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J282" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B283" t="s">
+        <v>952</v>
+      </c>
+      <c r="C283" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E283" t="s">
+        <v>955</v>
+      </c>
+      <c r="F283" t="s">
+        <v>956</v>
+      </c>
+      <c r="G283" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H283" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I283" t="s">
+        <v>66</v>
+      </c>
+      <c r="J283" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D284" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E284" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G284" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H284" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="I284" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J284" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B285" t="s">
+        <v>952</v>
+      </c>
+      <c r="C285" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E285" t="s">
+        <v>955</v>
+      </c>
+      <c r="F285" t="s">
+        <v>956</v>
+      </c>
+      <c r="G285" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H285" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I285" t="s">
+        <v>66</v>
+      </c>
+      <c r="J285" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A286" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B286" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D286" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E286" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G286" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H286" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I286" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J286" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B287" t="s">
+        <v>952</v>
+      </c>
+      <c r="C287" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D287" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E287" t="s">
+        <v>955</v>
+      </c>
+      <c r="F287" t="s">
+        <v>956</v>
+      </c>
+      <c r="G287" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H287" t="s">
+        <v>1065</v>
+      </c>
+      <c r="I287" t="s">
+        <v>66</v>
+      </c>
+      <c r="J287" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B288" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C288" s="4" t="s">
         <v>1067</v>
       </c>
-      <c r="B261" t="s">
-        <v>943</v>
-      </c>
-      <c r="C261" t="s">
-        <v>926</v>
-      </c>
-      <c r="D261" t="s">
+      <c r="D288" s="4" t="s">
         <v>1068</v>
       </c>
-      <c r="E261" t="s">
-        <v>945</v>
-      </c>
-      <c r="F261" t="s">
-        <v>946</v>
-      </c>
-      <c r="G261" t="s">
+      <c r="E288" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G288" s="4" t="s">
         <v>1069</v>
       </c>
-      <c r="H261" t="s">
+      <c r="H288" s="4" t="s">
         <v>1070</v>
       </c>
-      <c r="I261" t="s">
-        <v>66</v>
-      </c>
-      <c r="J261" s="6" t="s">
+      <c r="I288" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J288" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B289" t="s">
+        <v>952</v>
+      </c>
+      <c r="C289" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D289" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E289" t="s">
+        <v>955</v>
+      </c>
+      <c r="F289" t="s">
+        <v>956</v>
+      </c>
+      <c r="G289" t="s">
+        <v>1073</v>
+      </c>
+      <c r="H289" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I289" t="s">
+        <v>66</v>
+      </c>
+      <c r="J289" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E290" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="G290" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H290" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I290" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J290" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B291" t="s">
+        <v>952</v>
+      </c>
+      <c r="C291" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D291" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E291" t="s">
+        <v>955</v>
+      </c>
+      <c r="F291" t="s">
+        <v>956</v>
+      </c>
+      <c r="G291" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H291" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I291" t="s">
+        <v>66</v>
+      </c>
+      <c r="J291" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A292" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="D292" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E292" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G292" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H292" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I292" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J292" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B293" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C293" t="s">
+        <v>953</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E293" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F293" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G293" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H293" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I293" t="s">
+        <v>66</v>
+      </c>
+      <c r="J293" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E294" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G294" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H294" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I294" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J294" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B295" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C295" t="s">
+        <v>953</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E295" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F295" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G295" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H295" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I295" t="s">
+        <v>66</v>
+      </c>
+      <c r="J295" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A296" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B296" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E296" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G296" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H296" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I296" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J296" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B297" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C297" t="s">
+        <v>997</v>
+      </c>
+      <c r="D297" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E297" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F297" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G297" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H297" t="s">
+        <v>1109</v>
+      </c>
+      <c r="I297" t="s">
+        <v>66</v>
+      </c>
+      <c r="J297" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A298" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E298" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G298" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H298" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I298" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J298" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C299" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D299" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E299" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F299" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G299" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H299" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I299" t="s">
+        <v>84</v>
+      </c>
+      <c r="J299" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A300" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E300" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G300" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H300" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I300" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J300" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B301" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C301" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D301" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E301" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F301" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G301" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H301" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I301" t="s">
+        <v>84</v>
+      </c>
+      <c r="J301" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E302" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G302" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H302" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="I302" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J302" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C303" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D303" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E303" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F303" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G303" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H303" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I303" t="s">
+        <v>66</v>
+      </c>
+      <c r="J303" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E304" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G304" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H304" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="I304" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J304" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B305" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C305" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E305" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F305" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G305" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H305" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I305" t="s">
+        <v>66</v>
+      </c>
+      <c r="J305" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B306" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E306" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F306" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G306" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H306" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I306" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J306" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B307" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C307" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D307" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E307" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F307" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G307" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H307" t="s">
+        <v>1153</v>
+      </c>
+      <c r="I307" t="s">
+        <v>84</v>
+      </c>
+      <c r="J307" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E308" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G308" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H308" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I308" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J308" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C309" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D309" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E309" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F309" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G309" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H309" t="s">
+        <v>1161</v>
+      </c>
+      <c r="I309" t="s">
+        <v>84</v>
+      </c>
+      <c r="J309" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G310" s="4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H310" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I310" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J310" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C311" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D311" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E311" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F311" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G311" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H311" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I311" t="s">
+        <v>84</v>
+      </c>
+      <c r="J311" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="E312" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G312" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H312" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I312" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J312" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B313" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C313" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D313" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E313" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F313" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G313" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H313" t="s">
+        <v>1177</v>
+      </c>
+      <c r="I313" t="s">
+        <v>66</v>
+      </c>
+      <c r="J313" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E314" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G314" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H314" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I314" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J314" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B315" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C315" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D315" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E315" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F315" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G315" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H315" t="s">
+        <v>1186</v>
+      </c>
+      <c r="I315" t="s">
+        <v>66</v>
+      </c>
+      <c r="J315" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E316" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G316" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H316" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="I316" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J316" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B317" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C317" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D317" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E317" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F317" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G317" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H317" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I317" t="s">
+        <v>84</v>
+      </c>
+      <c r="J317" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G318" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="I318" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J318" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B319" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C319" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D319" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E319" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F319" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G319" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H319" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I319" t="s">
+        <v>66</v>
+      </c>
+      <c r="J319" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E320" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G320" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H320" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="I320" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J320" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B321" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C321" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D321" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E321" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F321" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G321" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H321" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I321" t="s">
+        <v>66</v>
+      </c>
+      <c r="J321" s="6" t="s">
         <v>67</v>
       </c>
     </row>
@@ -12869,19 +15257,19 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1071</v>
+        <v>1212</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1072</v>
+        <v>1213</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1073</v>
+        <v>1214</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1074</v>
+        <v>1215</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>56</v>
@@ -12892,16 +15280,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1075</v>
+        <v>1216</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>1076</v>
+        <v>1217</v>
       </c>
       <c r="E2" t="s">
         <v>66</v>
@@ -12910,21 +15298,21 @@
         <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>1077</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1078</v>
+        <v>1219</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>301</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>1079</v>
+        <v>1220</v>
       </c>
       <c r="E3" t="s">
         <v>66</v>
@@ -12933,21 +15321,21 @@
         <v>66</v>
       </c>
       <c r="G3" t="s">
-        <v>1077</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1080</v>
+        <v>1221</v>
       </c>
       <c r="B4" t="s">
-        <v>396</v>
+        <v>656</v>
       </c>
       <c r="C4" t="s">
-        <v>397</v>
+        <v>635</v>
       </c>
       <c r="D4" t="s">
-        <v>1081</v>
+        <v>1222</v>
       </c>
       <c r="E4" t="s">
         <v>66</v>
@@ -12956,44 +15344,44 @@
         <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>1077</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1082</v>
+        <v>1223</v>
       </c>
       <c r="B5" t="s">
-        <v>834</v>
+        <v>980</v>
       </c>
       <c r="C5" t="s">
-        <v>811</v>
+        <v>952</v>
       </c>
       <c r="D5" t="s">
-        <v>1083</v>
+        <v>1224</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>1077</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1084</v>
+        <v>1225</v>
       </c>
       <c r="B6" t="s">
-        <v>1004</v>
+        <v>1071</v>
       </c>
       <c r="C6" t="s">
-        <v>943</v>
+        <v>952</v>
       </c>
       <c r="D6" t="s">
-        <v>1085</v>
+        <v>1226</v>
       </c>
       <c r="E6" t="s">
         <v>66</v>
@@ -13002,7 +15390,7 @@
         <v>66</v>
       </c>
       <c r="G6" t="s">
-        <v>1077</v>
+        <v>1218</v>
       </c>
     </row>
   </sheetData>
@@ -13027,19 +15415,19 @@
         <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1086</v>
+        <v>1227</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1087</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -13056,10 +15444,10 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>1088</v>
+        <v>1229</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1089</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -13076,10 +15464,10 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>1090</v>
+        <v>1231</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1089</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -13096,10 +15484,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>1091</v>
+        <v>1232</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1089</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -13116,7 +15504,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>1092</v>
+        <v>1233</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>66</v>
@@ -13136,10 +15524,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>1090</v>
+        <v>1231</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1089</v>
+        <v>1230</v>
       </c>
     </row>
   </sheetData>
